--- a/Security Project - 복사본/KISA-AutoPatcher-Python/dist/reports/Security_Patch_Report.xlsx
+++ b/Security Project - 복사본/KISA-AutoPatcher-Python/dist/reports/Security_Patch_Report.xlsx
@@ -857,12 +857,12 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>불필요한 계정 없음</t>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
@@ -1101,10 +1101,14 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
       <c r="J16" s="0" t="inlineStr">
         <is>
@@ -1194,10 +1198,14 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="0" t="inlineStr">
         <is>
@@ -1255,10 +1263,14 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
       <c r="N21" s="0" t="inlineStr">
         <is>
@@ -1307,12 +1319,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>DHCP, DNS 클라이언트 X</t>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
         </is>
       </c>
       <c r="I23" s="6" t="n"/>
@@ -1368,10 +1380,15 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>W-20: 취약(현재값=Error: powershell.exe failed (1): #&lt; CLIXML
+&lt;Objs Version="1.1.0.1" xmlns="http://schemas.microsoft.com/powershell/2004/04"&gt;&lt;Obj S="progress" RefId="0"&gt;&lt;TN RefId="0"&gt;&lt;T&gt;System.Management.Automation.PSCustomObject&lt;/T&gt;&lt;T&gt;System.Object&lt;/T&gt;&lt;/TN&gt;&lt;MS&gt;&lt;I64 N="SourceId"&gt;1&lt;/I64&gt;&lt;PR N="Record"&gt;&lt;AV&gt;처음 사용하기 위해 모듈을 준비하는 중입니다.&lt;/AV&gt;&lt;AI&gt;0&lt;/AI&gt;&lt;Nil /&gt;&lt;PI&gt;-1&lt;/PI&gt;&lt;PC&gt;-1&lt;/PC&gt;&lt;T&gt;Completed&lt;/T&gt;&lt;SR&gt;-1&lt;/SR&gt;&lt;SD&gt; &lt;/SD&gt;&lt;/PR&gt;&lt;/MS&gt;&lt;/Obj&gt;&lt;Obj S="progress" RefId="1"&gt;&lt;TNRef RefId="0" /&gt;&lt;MS&gt;&lt;I64 N="SourceId"&gt;1&lt;/I64&gt;&lt;PR N="Record"&gt;&lt;AV&gt;처음 사용하기 위해 모듈을 준비하는 중입니다.&lt;/AV&gt;&lt;AI&gt;0&lt;/AI&gt;&lt;Nil /&gt;&lt;PI&gt;-1&lt;/PI&gt;&lt;PC&gt;-1&lt;/PC&gt;&lt;T&gt;Completed&lt;/T&gt;&lt;SR&gt;-1&lt;/SR&gt;&lt;SD&gt; &lt;/SD&gt;&lt;/PR&gt;&lt;/MS&gt;&lt;/Obj&gt;&lt;S S="Error"&gt;Select-Object : "SettingID" 속성을 찾을 수 없습니다._x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;위치 줄:1 문자:286_x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;+ ... Adapter -eq $true } | Select-Object -ExpandProperty SettingID); if ($ ..._x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;+                           ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~_x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;    + CategoryInfo          : InvalidArgument: (\\DESKTOP-BKBAM...r.DeviceID="12":PSObject) [Select-Object], PSArgumen _x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;   tException_x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;    + FullyQualifiedErrorId : ExpandPropertyNotFound,Microsoft.PowerShell.Commands.SelectObjectCommand_x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt; _x000D__x000A_&lt;/S&gt;&lt;/Objs&gt;)</t>
+        </is>
+      </c>
       <c r="I25" s="6" t="n"/>
       <c r="J25" s="0" t="inlineStr">
         <is>
@@ -1672,12 +1689,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>DNS 서버 X</t>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1731,12 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Telnet 사용 X</t>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
         </is>
       </c>
     </row>
@@ -1756,10 +1773,14 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="33" t="n"/>
@@ -1775,10 +1796,14 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="31" t="inlineStr">
@@ -1817,10 +1842,14 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="31" t="inlineStr">
@@ -1840,10 +1869,14 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="32" t="n"/>
@@ -1878,10 +1911,14 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="33" t="n"/>
@@ -1958,10 +1995,14 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="32" t="n"/>
@@ -2015,10 +2056,15 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr"/>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>W-52: 취약(현재값=Error: powershell.exe failed (1): #&lt; CLIXML
+&lt;Objs Version="1.1.0.1" xmlns="http://schemas.microsoft.com/powershell/2004/04"&gt;&lt;Obj S="progress" RefId="0"&gt;&lt;TN RefId="0"&gt;&lt;T&gt;System.Management.Automation.PSCustomObject&lt;/T&gt;&lt;T&gt;System.Object&lt;/T&gt;&lt;/TN&gt;&lt;MS&gt;&lt;I64 N="SourceId"&gt;1&lt;/I64&gt;&lt;PR N="Record"&gt;&lt;AV&gt;처음 사용하기 위해 모듈을 준비하는 중입니다.&lt;/AV&gt;&lt;AI&gt;0&lt;/AI&gt;&lt;Nil /&gt;&lt;PI&gt;-1&lt;/PI&gt;&lt;PC&gt;-1&lt;/PC&gt;&lt;T&gt;Completed&lt;/T&gt;&lt;SR&gt;-1&lt;/SR&gt;&lt;SD&gt; &lt;/SD&gt;&lt;/PR&gt;&lt;/MS&gt;&lt;/Obj&gt;&lt;S S="Error"&gt;null 값 식에서 메서드를 호출할 수 없습니다._x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;위치 줄:1 문자:93_x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;+ ... ng]::new(); (Get-ItemProperty -Path 'HKLM:\Software\Microsoft\Windows ..._x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;+                 ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~_x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;    + CategoryInfo          : InvalidOperation: (:) [], ParentContainsErrorRecordException_x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt;    + FullyQualifiedErrorId : InvokeMethodOnNull_x000D__x000A_&lt;/S&gt;&lt;S S="Error"&gt; _x000D__x000A_&lt;/S&gt;&lt;/Objs&gt;)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="B55" s="32" t="n"/>
@@ -2129,10 +2175,14 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="B61" s="32" t="n"/>
@@ -2186,10 +2236,14 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="B64" s="32" t="n"/>
@@ -2205,10 +2259,14 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="n"/>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>수동 검토 항목: 자동 적합 판정 없음</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="B65" s="32" t="n"/>
